--- a/MainTop/11.05.2026 Макс ВБ/print_new_print_sorted.xlsx
+++ b/MainTop/11.05.2026 Макс ВБ/print_new_print_sorted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\11.05.2026 Макс ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5933D8D7-D560-40BD-B638-9824EB3B2A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37ACF24-C977-4D1E-81F0-7660A73FF816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="67">
   <si>
     <t>Артикул</t>
   </si>
@@ -221,9 +221,6 @@
   </si>
   <si>
     <t>Термонаклейка Тигр розовый крупный план</t>
-  </si>
-  <si>
-    <t>в 4 города</t>
   </si>
 </sst>
 </file>
@@ -276,7 +273,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -306,17 +303,6 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -327,16 +313,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -652,28 +635,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>67</v>
-      </c>
+      <c r="E1" s="5"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="1">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -681,17 +662,14 @@
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="7">
-        <f>B2/4</f>
-        <v>12</v>
-      </c>
+      <c r="E2" s="6"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="1">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -699,17 +677,14 @@
       <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="7">
-        <f t="shared" ref="E3:E59" si="0">B3/4</f>
-        <v>9</v>
-      </c>
+      <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="1">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -717,17 +692,14 @@
       <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="7">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
+      <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="1">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
@@ -735,17 +707,14 @@
       <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="7">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
+      <c r="E5" s="6"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="1">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
@@ -753,17 +722,14 @@
       <c r="D6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="7">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
+      <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
@@ -771,17 +737,14 @@
       <c r="D7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
+      <c r="E7" s="6"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>5</v>
@@ -789,17 +752,14 @@
       <c r="D8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
+      <c r="E8" s="6"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
@@ -807,17 +767,14 @@
       <c r="D9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
+      <c r="E9" s="6"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
@@ -825,17 +782,14 @@
       <c r="D10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
+      <c r="E10" s="6"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="1">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
@@ -843,17 +797,14 @@
       <c r="D11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="7">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
+      <c r="E11" s="6"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="1">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>5</v>
@@ -861,17 +812,14 @@
       <c r="D12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="7">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
+      <c r="E12" s="6"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="1">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>5</v>
@@ -879,17 +827,14 @@
       <c r="D13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="7">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
+      <c r="E13" s="6"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B14" s="1">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>5</v>
@@ -897,17 +842,14 @@
       <c r="D14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E14" s="7">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
+      <c r="E14" s="6"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="1">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>5</v>
@@ -915,17 +857,14 @@
       <c r="D15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E15" s="7">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
+      <c r="E15" s="6"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B16" s="2">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>5</v>
@@ -933,17 +872,14 @@
       <c r="D16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E16" s="7">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
+      <c r="E16" s="6"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>5</v>
@@ -951,17 +887,14 @@
       <c r="D17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E17" s="7">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
+      <c r="E17" s="6"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>5</v>
@@ -969,17 +902,14 @@
       <c r="D18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E18" s="7">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
+      <c r="E18" s="6"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>5</v>
@@ -987,17 +917,14 @@
       <c r="D19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E19" s="7">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
+      <c r="E19" s="6"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B20" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>5</v>
@@ -1005,17 +932,14 @@
       <c r="D20" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E20" s="7">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
+      <c r="E20" s="6"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B21" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>5</v>
@@ -1023,17 +947,14 @@
       <c r="D21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E21" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E21" s="6"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B22" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>5</v>
@@ -1041,17 +962,14 @@
       <c r="D22" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E22" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E22" s="6"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B23" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>5</v>
@@ -1059,17 +977,14 @@
       <c r="D23" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E23" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E23" s="6"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B24" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>5</v>
@@ -1077,17 +992,14 @@
       <c r="D24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E24" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E24" s="6"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B25" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>5</v>
@@ -1095,17 +1007,14 @@
       <c r="D25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E25" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E25" s="6"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B26" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>5</v>
@@ -1113,17 +1022,14 @@
       <c r="D26" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E26" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E26" s="6"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B27" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>5</v>
@@ -1131,17 +1037,14 @@
       <c r="D27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E27" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E27" s="6"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B28" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>5</v>
@@ -1149,17 +1052,14 @@
       <c r="D28" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E28" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E28" s="6"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B29" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>5</v>
@@ -1167,17 +1067,14 @@
       <c r="D29" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E29" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E29" s="6"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B30" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>5</v>
@@ -1185,17 +1082,14 @@
       <c r="D30" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E30" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E30" s="6"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B31" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>5</v>
@@ -1203,17 +1097,14 @@
       <c r="D31" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E31" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E31" s="6"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B32" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>5</v>
@@ -1221,17 +1112,14 @@
       <c r="D32" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E32" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E32" s="6"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B33" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>5</v>
@@ -1239,17 +1127,14 @@
       <c r="D33" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E33" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E33" s="6"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B34" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>5</v>
@@ -1257,17 +1142,14 @@
       <c r="D34" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E34" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E34" s="6"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B35" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>5</v>
@@ -1275,17 +1157,14 @@
       <c r="D35" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E35" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E35" s="6"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B36" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>5</v>
@@ -1293,17 +1172,14 @@
       <c r="D36" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E36" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E36" s="6"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B37" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>5</v>
@@ -1311,17 +1187,14 @@
       <c r="D37" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E37" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E37" s="6"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B38" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>5</v>
@@ -1329,17 +1202,14 @@
       <c r="D38" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E38" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E38" s="6"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B39" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>44</v>
@@ -1347,17 +1217,14 @@
       <c r="D39" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E39" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
+      <c r="E39" s="6"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B40" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>44</v>
@@ -1365,17 +1232,14 @@
       <c r="D40" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E40" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
+      <c r="E40" s="6"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B41" s="2">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>44</v>
@@ -1383,17 +1247,14 @@
       <c r="D41" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E41" s="7">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
+      <c r="E41" s="6"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B42" s="2">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>44</v>
@@ -1401,17 +1262,14 @@
       <c r="D42" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E42" s="7">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
+      <c r="E42" s="6"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B43" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>44</v>
@@ -1419,17 +1277,14 @@
       <c r="D43" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E43" s="7">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
+      <c r="E43" s="6"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B44" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>44</v>
@@ -1437,17 +1292,14 @@
       <c r="D44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E44" s="7">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
+      <c r="E44" s="6"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B45" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>44</v>
@@ -1455,17 +1307,14 @@
       <c r="D45" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E45" s="7">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
+      <c r="E45" s="6"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B46" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>44</v>
@@ -1473,17 +1322,14 @@
       <c r="D46" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E46" s="7">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
+      <c r="E46" s="6"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B47" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>44</v>
@@ -1491,17 +1337,14 @@
       <c r="D47" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E47" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E47" s="6"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B48" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>44</v>
@@ -1509,17 +1352,14 @@
       <c r="D48" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E48" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E48" s="6"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B49" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>44</v>
@@ -1527,17 +1367,14 @@
       <c r="D49" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E49" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E49" s="6"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B50" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>44</v>
@@ -1545,17 +1382,14 @@
       <c r="D50" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E50" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E50" s="6"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B51" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>44</v>
@@ -1563,17 +1397,14 @@
       <c r="D51" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E51" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E51" s="6"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>57</v>
       </c>
       <c r="B52" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>44</v>
@@ -1581,17 +1412,14 @@
       <c r="D52" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E52" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E52" s="6"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>58</v>
       </c>
       <c r="B53" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>44</v>
@@ -1599,17 +1427,14 @@
       <c r="D53" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E53" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E53" s="6"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>59</v>
       </c>
       <c r="B54" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>44</v>
@@ -1617,17 +1442,14 @@
       <c r="D54" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E54" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E54" s="6"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B55" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>44</v>
@@ -1635,17 +1457,14 @@
       <c r="D55" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E55" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E55" s="6"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>61</v>
       </c>
       <c r="B56" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>44</v>
@@ -1653,17 +1472,14 @@
       <c r="D56" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E56" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E56" s="6"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>62</v>
       </c>
       <c r="B57" s="3">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>63</v>
@@ -1671,17 +1487,14 @@
       <c r="D57" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E57" s="7">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
+      <c r="E57" s="6"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>64</v>
       </c>
       <c r="B58" s="4">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>65</v>
@@ -1689,17 +1502,14 @@
       <c r="D58" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E58" s="7">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
+      <c r="E58" s="6"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>66</v>
       </c>
       <c r="B59" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>65</v>
@@ -1707,10 +1517,7 @@
       <c r="D59" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E59" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="E59" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/MainTop/11.05.2026 Макс ВБ/print_new_print_sorted.xlsx
+++ b/MainTop/11.05.2026 Макс ВБ/print_new_print_sorted.xlsx
@@ -5,17 +5,28 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\11.05.2026 Макс ВБ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\11.05.2026 Макс ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5933D8D7-D560-40BD-B638-9824EB3B2A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECCD7DDB-B013-46F3-AD56-B82CE44D041C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -327,7 +338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -340,6 +351,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -642,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.7109375" customWidth="1"/>
@@ -1712,7 +1724,14 @@
         <v>2</v>
       </c>
     </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E60" s="8">
+        <f>SUM(E2:E59)</f>
+        <v>204</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>